--- a/salidas/empresas/BRK-B.xlsx
+++ b/salidas/empresas/BRK-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1381,7 +1393,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1406,7 +1418,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1431,7 +1443,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1456,7 +1468,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1481,7 +1493,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1506,7 +1518,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1531,7 +1543,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1556,7 +1568,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1581,7 +1593,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1606,7 +1618,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1631,7 +1643,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1656,7 +1668,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1681,7 +1693,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1706,7 +1718,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1731,7 +1743,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1760,7 +1772,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1789,7 +1801,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1818,7 +1830,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1847,7 +1859,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1876,7 +1888,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1905,7 +1917,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1934,7 +1946,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1963,7 +1975,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1992,7 +2004,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2021,7 +2033,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2040,7 +2052,7 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2059,7 +2071,7 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2082,7 +2094,7 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2105,7 +2117,7 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2128,7 +2140,7 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2151,7 +2163,7 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2174,7 +2186,7 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2197,7 +2209,7 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2226,7 +2238,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2255,7 +2267,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2280,7 +2292,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2305,7 +2317,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2330,7 +2342,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2355,7 +2367,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2380,7 +2392,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2409,7 +2421,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2438,7 +2450,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2467,7 +2479,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2496,7 +2508,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2525,7 +2537,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2554,7 +2566,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2583,7 +2595,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2612,7 +2624,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2641,7 +2653,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2670,7 +2682,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2699,7 +2711,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2728,7 +2740,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2757,7 +2769,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2786,7 +2798,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2815,7 +2827,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2844,7 +2856,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2873,7 +2885,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2902,7 +2914,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -2931,7 +2943,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2960,7 +2972,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3018,7 +3030,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3047,7 +3059,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3076,7 +3088,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3105,7 +3117,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3134,7 +3146,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3163,7 +3175,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3192,7 +3204,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3221,7 +3233,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3250,7 +3262,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3279,7 +3291,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3337,7 +3349,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3366,7 +3378,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3395,7 +3407,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3424,7 +3436,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3453,7 +3465,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3482,7 +3494,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3511,7 +3523,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3530,7 +3542,7 @@
       <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3549,7 +3561,7 @@
       <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3568,7 +3580,7 @@
       <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3587,7 +3599,7 @@
       <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3606,7 +3618,7 @@
       <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3625,7 +3637,7 @@
       <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3644,7 +3656,7 @@
       <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3663,7 +3675,7 @@
       <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3682,7 +3694,7 @@
       <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3701,7 +3713,7 @@
       <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3720,7 +3732,7 @@
       <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3739,7 +3751,7 @@
       <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3758,7 +3770,7 @@
       <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3777,7 +3789,7 @@
       <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -3796,7 +3808,7 @@
       <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3815,7 +3827,7 @@
       <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -3834,7 +3846,7 @@
       <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -3853,7 +3865,7 @@
       <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -3872,7 +3884,7 @@
       <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -3891,7 +3903,7 @@
       <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -3910,7 +3922,7 @@
       <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -3929,7 +3941,7 @@
       <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -3948,7 +3960,7 @@
       <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -3967,7 +3979,7 @@
       <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -3986,7 +3998,7 @@
       <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4005,7 +4017,7 @@
       <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4024,7 +4036,7 @@
       <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4043,7 +4055,7 @@
       <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4062,7 +4074,7 @@
       <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4081,7 +4093,7 @@
       <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4100,7 +4112,7 @@
       <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4119,7 +4131,7 @@
       <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4138,7 +4150,7 @@
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4157,7 +4169,7 @@
       <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4176,7 +4188,7 @@
       <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4195,7 +4207,7 @@
       <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4214,7 +4226,7 @@
       <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4233,7 +4245,7 @@
       <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4252,7 +4264,7 @@
       <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4271,7 +4283,7 @@
       <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4290,7 +4302,7 @@
       <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4309,7 +4321,7 @@
       <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4328,7 +4340,7 @@
       <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4347,7 +4359,7 @@
       <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4366,7 +4378,7 @@
       <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4385,7 +4397,7 @@
       <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4404,7 +4416,7 @@
       <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4423,7 +4435,7 @@
       <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4442,7 +4454,7 @@
       <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4461,7 +4473,7 @@
       <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4480,7 +4492,7 @@
       <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -4499,7 +4511,7 @@
       <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -4518,7 +4530,7 @@
       <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -4537,7 +4549,7 @@
       <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -4556,7 +4568,7 @@
       <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -4575,7 +4587,7 @@
       <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -4594,7 +4606,7 @@
       <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -4613,7 +4625,7 @@
       <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -4632,7 +4644,7 @@
       <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -4651,7 +4663,7 @@
       <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -4670,7 +4682,7 @@
       <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -4689,7 +4701,7 @@
       <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -4708,7 +4720,7 @@
       <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -4727,7 +4739,7 @@
       <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -4746,7 +4758,7 @@
       <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -4765,7 +4777,7 @@
       <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -4784,7 +4796,7 @@
       <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -4803,7 +4815,7 @@
       <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -4822,7 +4834,7 @@
       <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -4841,7 +4853,7 @@
       <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -4860,7 +4872,7 @@
       <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -4879,7 +4891,7 @@
       <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -4898,7 +4910,7 @@
       <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -4917,7 +4929,7 @@
       <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -4936,7 +4948,7 @@
       <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -4955,7 +4967,7 @@
       <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -4974,7 +4986,7 @@
       <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -4993,7 +5005,7 @@
       <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5012,7 +5024,7 @@
       <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5031,7 +5043,7 @@
       <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5050,7 +5062,7 @@
       <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5069,7 +5081,7 @@
       <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5088,7 +5100,7 @@
       <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5107,7 +5119,7 @@
       <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5126,7 +5138,7 @@
       <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5145,7 +5157,7 @@
       <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -5164,7 +5176,7 @@
       <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -5183,7 +5195,7 @@
       <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -5202,7 +5214,7 @@
       <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -5221,7 +5233,7 @@
       <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -5240,7 +5252,7 @@
       <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -5259,7 +5271,7 @@
       <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -5278,7 +5290,7 @@
       <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -5297,7 +5309,7 @@
       <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -5316,7 +5328,7 @@
       <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -5335,7 +5347,7 @@
       <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -5354,7 +5366,7 @@
       <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -5373,7 +5385,7 @@
       <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -5392,7 +5404,7 @@
       <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -5411,7 +5423,7 @@
       <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -5430,7 +5442,7 @@
       <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -5449,7 +5461,7 @@
       <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -5468,7 +5480,7 @@
       <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -5487,7 +5499,7 @@
       <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -5506,7 +5518,7 @@
       <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -5525,7 +5537,7 @@
       <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -5544,7 +5556,7 @@
       <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -5563,7 +5575,7 @@
       <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -5582,7 +5594,7 @@
       <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -5601,7 +5613,7 @@
       <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -5620,7 +5632,7 @@
       <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -5639,7 +5651,7 @@
       <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -5658,7 +5670,7 @@
       <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -5677,7 +5689,7 @@
       <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -5696,7 +5708,7 @@
       <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -5715,7 +5727,7 @@
       <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -5734,7 +5746,7 @@
       <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -5753,7 +5765,7 @@
       <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -5772,7 +5784,7 @@
       <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -5791,7 +5803,7 @@
       <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -5810,7 +5822,7 @@
       <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -5829,7 +5841,7 @@
       <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -5848,17 +5860,17 @@
       <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>507.1700134277344</v>
+        <v>505.1799926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>507.1700134277344</v>
+        <v>505.1799926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>76794800</v>
+        <v>79496000</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
@@ -5895,75 +5907,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5999,13 +6011,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6041,13 +6053,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6083,13 +6095,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6125,13 +6137,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6158,7 +6170,7 @@
       <c r="I6" t="n">
         <v>3.459328243463572</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K6" t="n">
@@ -6171,13 +6183,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6204,7 +6216,7 @@
       <c r="I7" t="n">
         <v>5.633871839943337</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -6217,13 +6229,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6250,7 +6262,7 @@
       <c r="I8" t="n">
         <v>5.01520517327667</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -6263,13 +6275,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6296,7 +6308,7 @@
       <c r="I9" t="n">
         <v>4.833205173276671</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -6309,13 +6321,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6342,7 +6354,7 @@
       <c r="I10" t="n">
         <v>5.29120517327667</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -6355,13 +6367,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6388,7 +6400,7 @@
       <c r="I11" t="n">
         <v>4.387760218780389</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -6401,13 +6413,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6434,7 +6446,7 @@
       <c r="I12" t="n">
         <v>4.972426885447056</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K12" t="n">
@@ -6447,13 +6459,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6480,7 +6492,7 @@
       <c r="I13" t="n">
         <v>4.683093552113722</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K13" t="n">
@@ -6493,13 +6505,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6526,7 +6538,7 @@
       <c r="I14" t="n">
         <v>4.143093552113722</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K14" t="n">
@@ -6539,13 +6551,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6572,7 +6584,7 @@
       <c r="I15" t="n">
         <v>4.842666666666666</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K15" t="n">
@@ -6585,13 +6597,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6618,7 +6630,7 @@
       <c r="I16" t="n">
         <v>4.715941991707393</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K16" t="n">
@@ -6631,13 +6643,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6664,7 +6676,7 @@
       <c r="I17" t="n">
         <v>5.377686720704485</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K17" t="n">
@@ -6677,13 +6689,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6710,7 +6722,7 @@
       <c r="I18" t="n">
         <v>5.985020054037819</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K18" t="n">
@@ -6723,13 +6735,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6756,7 +6768,7 @@
       <c r="I19" t="n">
         <v>6.659121549450274</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K19" t="n">
@@ -6769,13 +6781,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6802,7 +6814,7 @@
       <c r="I20" t="n">
         <v>7.246405793988259</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K20" t="n">
@@ -6815,13 +6827,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6848,7 +6860,7 @@
       <c r="I21" t="n">
         <v>7.714003869995164</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K21" t="n">
@@ -6861,13 +6873,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6894,7 +6906,7 @@
       <c r="I22" t="n">
         <v>7.899337203328498</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="K22" t="n">
@@ -6907,13 +6919,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6940,7 +6952,7 @@
       <c r="I23" t="n">
         <v>7.822448665196367</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K23" t="n">
@@ -6953,13 +6965,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6986,7 +6998,7 @@
       <c r="I24" t="n">
         <v>8.57324070139981</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="K24" t="n">
@@ -6999,13 +7011,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7032,7 +7044,7 @@
       <c r="I25" t="n">
         <v>8.397804327706</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K25" t="n">
@@ -7045,13 +7057,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7078,7 +7090,7 @@
       <c r="I26" t="n">
         <v>8.059943559503708</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K26" t="n">
@@ -7091,13 +7103,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7124,7 +7136,7 @@
       <c r="I27" t="n">
         <v>8.247480455383947</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K27" t="n">
@@ -7137,13 +7149,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7170,7 +7182,7 @@
       <c r="I28" t="n">
         <v>7.283034445826127</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K28" t="n">
@@ -7183,13 +7195,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7216,7 +7228,7 @@
       <c r="I29" t="n">
         <v>9.233914807398948</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K29" t="n">
@@ -7254,57 +7266,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C2" t="n">
@@ -7338,10 +7350,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -7375,10 +7387,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39447</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C4" t="n">
@@ -7412,10 +7424,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C5" t="n">
@@ -7449,10 +7461,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C6" t="n">
@@ -7486,10 +7498,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C7" t="n">
@@ -7523,10 +7535,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C8" t="n">
@@ -7560,10 +7572,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C9" t="n">
@@ -7597,10 +7609,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C10" t="n">
@@ -7634,10 +7646,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C11" t="n">
@@ -7671,10 +7683,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C12" t="n">
@@ -7708,10 +7720,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C13" t="n">
@@ -7745,10 +7757,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C14" t="n">
@@ -7782,10 +7794,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -7819,10 +7831,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C16" t="n">
@@ -7856,10 +7868,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C17" t="n">
@@ -7893,10 +7905,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C18" t="n">
@@ -7930,10 +7942,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C19" t="n">
@@ -7967,10 +7979,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C20" t="n">
@@ -8004,10 +8016,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C21" t="n">
@@ -8041,10 +8053,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C22" t="n">
@@ -8078,10 +8090,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C23" t="n">
@@ -8115,10 +8127,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="C24" t="n">
@@ -8152,10 +8164,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C25" t="n">
@@ -8189,10 +8201,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C26" t="n">
@@ -8226,10 +8238,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C27" t="n">
@@ -8263,10 +8275,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="C28" t="n">
@@ -8300,10 +8312,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C29" t="n">
@@ -8337,10 +8349,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C30" t="n">
@@ -8374,10 +8386,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C31" t="n">
@@ -8429,12 +8441,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
